--- a/docs/excel-book/projets/Projet5-Tableau-de-bord-ventes.xlsx
+++ b/docs/excel-book/projets/Projet5-Tableau-de-bord-ventes.xlsx
@@ -709,11 +709,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="80909440"/>
-        <c:axId val="50768686"/>
+        <c:axId val="24785129"/>
+        <c:axId val="47464772"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="80909440"/>
+        <c:axId val="24785129"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -745,7 +745,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50768686"/>
+        <c:crossAx val="47464772"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -753,7 +753,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50768686"/>
+        <c:axId val="47464772"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -795,7 +795,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80909440"/>
+        <c:crossAx val="24785129"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1879,7 +1879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30866082-7F6B-4FF8-A4AA-F3F596AB44A6}</x14:id>
+          <x14:id>{CAE09525-29B5-489E-965D-38B8A49DAF25}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1902,7 +1902,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{30866082-7F6B-4FF8-A4AA-F3F596AB44A6}">
+          <x14:cfRule type="dataBar" id="{CAE09525-29B5-489E-965D-38B8A49DAF25}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
